--- a/TestCases/curl_data.xlsx
+++ b/TestCases/curl_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -45,17 +45,7 @@
         --url http://localhost:16067/encrypt \
         --header 'content-type: application/json' \
         --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
-        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|FAILED|Transaction failed|U30|NA|vpa|1074636|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">curl --request POST \
-        --url http://localhost:16067/encrypt \
-        --header 'content-type: application/json' \
-        --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
-        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|EXPIRED|Transaction Expired|02|NA|vpa|1074636|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
+        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|FAILED|Transaction failed|U30|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
   </si>
 </sst>
 </file>
@@ -65,7 +55,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -93,6 +83,13 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13.5"/>
+      <color rgb="FF000000"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
     <font>
       <b val="true"/>
@@ -152,7 +149,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -165,7 +162,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -208,32 +209,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="205.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="205.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3"/>
+      <c r="B16" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="curl --request POST \&#10;        --url http://localhost:16067/encrypt \&#10;        --header 'content-type: application/json' \&#10;        --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \&#10;        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|SUCCESS|Transaction success|00|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'"/>
+    <hyperlink ref="B2" r:id="rId1" display="http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>

--- a/TestCases/curl_data.xlsx
+++ b/TestCases/curl_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -47,16 +47,6 @@
         --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
         --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|FAILED|Transaction failed|U30|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
   </si>
-  <si>
-    <t xml:space="preserve">expire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">curl --request POST \
-        --url http://localhost:16067/encrypt \
-        --header 'content-type: application/json' \
-        --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
-        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|EXPIRED|Transaction Expired|02|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
-  </si>
 </sst>
 </file>
 
@@ -65,7 +55,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -93,6 +83,13 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13.5"/>
+      <color rgb="FF000000"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
     <font>
       <b val="true"/>
@@ -152,7 +149,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -165,7 +162,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -212,28 +213,16 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3"/>
+      <c r="B16" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="curl --request POST \&#10;        --url http://localhost:16067/encrypt \&#10;        --header 'content-type: application/json' \&#10;        --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \&#10;        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|SUCCESS|Transaction success|00|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'"/>
+    <hyperlink ref="B2" r:id="rId1" display="http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>

--- a/TestCases/curl_data.xlsx
+++ b/TestCases/curl_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -45,7 +45,17 @@
         --url http://localhost:16067/encrypt \
         --header 'content-type: application/json' \
         --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
-        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|FAILED|Transaction failed|U30|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
+        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|FAILED|Transaction failed|U30|NA|vpa|1074636|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curl --request POST \
+        --url http://localhost:16067/encrypt \
+        --header 'content-type: application/json' \
+        --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
+        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|EXPIRED|Transaction Expired|02|NA|vpa|1074636|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
   </si>
 </sst>
 </file>
@@ -55,7 +65,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -83,13 +93,6 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="13.5"/>
-      <color rgb="FF000000"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
     </font>
     <font>
       <b val="true"/>
@@ -149,7 +152,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -162,11 +165,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -209,20 +208,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="205.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
+    <row r="4" customFormat="false" ht="205.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4"/>
+      <c r="B16" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA"/>
+    <hyperlink ref="B2" r:id="rId1" display="curl --request POST \&#10;        --url http://localhost:16067/encrypt \&#10;        --header 'content-type: application/json' \&#10;        --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \&#10;        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|SUCCESS|Transaction success|00|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>

--- a/TestCases/curl_data.xlsx
+++ b/TestCases/curl_data.xlsx
@@ -45,7 +45,7 @@
         --url http://localhost:16067/encrypt \
         --header 'content-type: application/json' \
         --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
-        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|FAILED|Transaction failed|U30|NA|vpa|1074636|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
+        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|FAILED|Transaction failed|U30|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
   </si>
   <si>
     <t xml:space="preserve">expire</t>
@@ -55,7 +55,7 @@
         --url http://localhost:16067/encrypt \
         --header 'content-type: application/json' \
         --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
-        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|EXPIRED|Transaction Expired|02|NA|vpa|1074636|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
+        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|EXPIRED|Transaction Expired|02|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
   </si>
 </sst>
 </file>
@@ -208,7 +208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="205.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -216,7 +216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="205.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>6</v>
       </c>

--- a/TestCases/curl_data.xlsx
+++ b/TestCases/curl_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -56,6 +56,16 @@
         --header 'content-type: application/json' \
         --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
         --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|EXPIRED|Transaction Expired|02|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curl --request POST \
+        --url http://localhost:16067/encrypt \
+        --header 'content-type: application/json' \
+        --header 'enckey: 57c3f7c3b0d8dc0be189ec63f68fce42' \
+        --data '211115084892E010054916|Txn_id|amount|2020:06:29 02:59:40|PENDING|Transaction pending|01|NA|vpa|rrn|NA|null|null|null|null|null|Yes Bank Of India!00000003783965091!CBIN0284021!918650503915|PAY!http://www.npci.org.in/!NA!!Geetanjaliacnchi!NA!|amazonsellerservices.98397377@hdfcbank!NA!NA|NA|NA'</t>
   </si>
 </sst>
 </file>
@@ -224,7 +234,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
